--- a/docs/VFMaritalStatus.xlsx
+++ b/docs/VFMaritalStatus.xlsx
@@ -58,13 +58,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/VFMaritalStatus.xlsx
+++ b/docs/VFMaritalStatus.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
